--- a/docs/downloads/04/tbl_other_act_sex_alaotra_feramanga_atsimo.xlsx
+++ b/docs/downloads/04/tbl_other_act_sex_alaotra_feramanga_atsimo.xlsx
@@ -420,12 +420,6 @@
           <t>Chômeur</t>
         </is>
       </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -512,12 +506,6 @@
           <t>Éleveur</t>
         </is>
       </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -535,12 +523,6 @@
           <t>Étudiant</t>
         </is>
       </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -581,12 +563,6 @@
           <t>Chômeur</t>
         </is>
       </c>
-      <c r="D10">
-        <v>3</v>
-      </c>
-      <c r="E10">
-        <v>2.6</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -604,12 +580,6 @@
           <t>Commerçant</t>
         </is>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>0.9</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -811,12 +781,6 @@
           <t>Pêcheur exploitant</t>
         </is>
       </c>
-      <c r="D20">
-        <v>3</v>
-      </c>
-      <c r="E20">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -926,12 +890,6 @@
           <t>Commerçant</t>
         </is>
       </c>
-      <c r="D25">
-        <v>2</v>
-      </c>
-      <c r="E25">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -994,12 +952,6 @@
         <is>
           <t>Éleveur</t>
         </is>
-      </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-      <c r="E28">
-        <v>0.2</v>
       </c>
     </row>
     <row r="29">

--- a/docs/downloads/04/tbl_other_act_sex_alaotra_feramanga_atsimo.xlsx
+++ b/docs/downloads/04/tbl_other_act_sex_alaotra_feramanga_atsimo.xlsx
@@ -394,14 +394,8 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D2">
-        <v>53</v>
-      </c>
-      <c r="E2">
-        <v>39</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -417,8 +411,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chômeur</t>
-        </is>
+          <t>Commerce &amp; Restauration</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>13</v>
+      </c>
+      <c r="E3">
+        <v>14.4</v>
       </c>
     </row>
     <row r="4">
@@ -434,14 +434,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="E4">
-        <v>8.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="5">
@@ -457,14 +457,8 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>55</v>
-      </c>
-      <c r="E5">
-        <v>40.4</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -480,14 +474,8 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6">
-        <v>6.6</v>
+          <t>Elève / Etudiant</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -503,8 +491,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>9</v>
+      </c>
+      <c r="E7">
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -520,8 +514,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Étudiant</t>
-        </is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>6</v>
+      </c>
+      <c r="E8">
+        <v>6.7</v>
       </c>
     </row>
     <row r="9">
@@ -537,14 +537,8 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>76</v>
-      </c>
-      <c r="E9">
-        <v>66.7</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -560,7 +554,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
     </row>
@@ -577,8 +571,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>22</v>
+      </c>
+      <c r="E11">
+        <v>48.9</v>
       </c>
     </row>
     <row r="12">
@@ -594,14 +594,8 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>22</v>
-      </c>
-      <c r="E12">
-        <v>19.3</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -617,14 +611,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D13">
         <v>6</v>
       </c>
       <c r="E13">
-        <v>5.3</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="14">
@@ -640,37 +634,37 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D14">
         <v>6</v>
       </c>
       <c r="E14">
-        <v>5.3</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="D15">
-        <v>405</v>
+        <v>7</v>
       </c>
       <c r="E15">
-        <v>46.2</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="16">
@@ -686,14 +680,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="D16">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E16">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="17">
@@ -709,14 +703,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D17">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="E17">
-        <v>7.1</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="18">
@@ -732,14 +726,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D18">
         <v>289</v>
       </c>
       <c r="E18">
-        <v>33</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="19">
@@ -755,14 +749,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="D19">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="E19">
-        <v>6.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="20">
@@ -778,8 +772,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pêcheur exploitant</t>
-        </is>
+          <t>Elève / Etudiant</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>26</v>
+      </c>
+      <c r="E20">
+        <v>4.9</v>
       </c>
     </row>
     <row r="21">
@@ -795,14 +795,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D21">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="E21">
-        <v>0.9</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="22">
@@ -818,14 +818,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="D22">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -841,14 +841,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="D23">
-        <v>418</v>
+        <v>11</v>
       </c>
       <c r="E23">
-        <v>71.5</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="24">
@@ -864,14 +864,8 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chômeur</t>
-        </is>
-      </c>
-      <c r="D24">
-        <v>19</v>
-      </c>
-      <c r="E24">
-        <v>3.2</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -887,8 +881,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>101</v>
+      </c>
+      <c r="E25">
+        <v>47.6</v>
       </c>
     </row>
     <row r="26">
@@ -904,14 +904,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="D26">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c r="E26">
-        <v>17.3</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="27">
@@ -927,14 +927,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D27">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E27">
-        <v>3.2</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="28">
@@ -950,8 +950,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>19</v>
+      </c>
+      <c r="E28">
+        <v>9</v>
       </c>
     </row>
     <row r="29">
@@ -967,14 +973,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="D29">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E29">
-        <v>4.3</v>
+        <v>17.9</v>
       </c>
     </row>
   </sheetData>
